--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2880"/>
+  <dimension ref="A1:G2905"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -84724,6 +84724,781 @@
         </is>
       </c>
     </row>
+    <row r="2881">
+      <c r="A2881" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B2881" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="C2881" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2881" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2881" t="n">
+        <v>25.91</v>
+      </c>
+      <c r="F2881" t="n">
+        <v>6.478</v>
+      </c>
+      <c r="G2881" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2882">
+      <c r="A2882" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B2882" t="inlineStr">
+        <is>
+          <t>4221</t>
+        </is>
+      </c>
+      <c r="C2882" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2882" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2882" t="n">
+        <v>38.4</v>
+      </c>
+      <c r="F2882" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="G2882" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2883">
+      <c r="A2883" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B2883" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="C2883" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2883" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2883" t="n">
+        <v>28.78</v>
+      </c>
+      <c r="F2883" t="n">
+        <v>5.756</v>
+      </c>
+      <c r="G2883" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2884">
+      <c r="A2884" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="B2884" t="inlineStr">
+        <is>
+          <t>4316</t>
+        </is>
+      </c>
+      <c r="C2884" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2884" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2884" t="n">
+        <v>35.04</v>
+      </c>
+      <c r="F2884" t="n">
+        <v>5.84</v>
+      </c>
+      <c r="G2884" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2885">
+      <c r="A2885" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B2885" t="inlineStr">
+        <is>
+          <t>1229</t>
+        </is>
+      </c>
+      <c r="C2885" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2885" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2885" t="n">
+        <v>177.88</v>
+      </c>
+      <c r="F2885" t="n">
+        <v>6.134</v>
+      </c>
+      <c r="G2885" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2886">
+      <c r="A2886" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B2886" t="inlineStr">
+        <is>
+          <t>2205</t>
+        </is>
+      </c>
+      <c r="C2886" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2886" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2886" t="n">
+        <v>34.87</v>
+      </c>
+      <c r="F2886" t="n">
+        <v>8.717000000000001</v>
+      </c>
+      <c r="G2886" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2887">
+      <c r="A2887" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B2887" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="C2887" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2887" t="n">
+        <v>77</v>
+      </c>
+      <c r="E2887" t="n">
+        <v>572.14</v>
+      </c>
+      <c r="F2887" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="G2887" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2888">
+      <c r="A2888" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B2888" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="C2888" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2888" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2888" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="F2888" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="G2888" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2889">
+      <c r="A2889" t="inlineStr">
+        <is>
+          <t>2026-08-12</t>
+        </is>
+      </c>
+      <c r="B2889" t="inlineStr">
+        <is>
+          <t>5624</t>
+        </is>
+      </c>
+      <c r="C2889" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2889" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2889" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="F2889" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="G2889" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2890">
+      <c r="A2890" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B2890" t="inlineStr">
+        <is>
+          <t>4105</t>
+        </is>
+      </c>
+      <c r="C2890" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2890" t="n">
+        <v>24</v>
+      </c>
+      <c r="E2890" t="n">
+        <v>199.19</v>
+      </c>
+      <c r="F2890" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="G2890" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2891">
+      <c r="A2891" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="B2891" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="C2891" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2891" t="n">
+        <v>159</v>
+      </c>
+      <c r="E2891" t="n">
+        <v>986.41</v>
+      </c>
+      <c r="F2891" t="n">
+        <v>6.204</v>
+      </c>
+      <c r="G2891" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2892">
+      <c r="A2892" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2892" t="inlineStr">
+        <is>
+          <t>5193</t>
+        </is>
+      </c>
+      <c r="C2892" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2892" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2892" t="n">
+        <v>13.42</v>
+      </c>
+      <c r="F2892" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="G2892" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2893">
+      <c r="A2893" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2893" t="inlineStr">
+        <is>
+          <t>5412</t>
+        </is>
+      </c>
+      <c r="C2893" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2893" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2893" t="n">
+        <v>275.4</v>
+      </c>
+      <c r="F2893" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="G2893" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2894">
+      <c r="A2894" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2894" t="inlineStr">
+        <is>
+          <t>5823</t>
+        </is>
+      </c>
+      <c r="C2894" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2894" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2894" t="n">
+        <v>33.8</v>
+      </c>
+      <c r="F2894" t="n">
+        <v>6.76</v>
+      </c>
+      <c r="G2894" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2895">
+      <c r="A2895" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2895" t="inlineStr">
+        <is>
+          <t>5824</t>
+        </is>
+      </c>
+      <c r="C2895" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2895" t="n">
+        <v>135</v>
+      </c>
+      <c r="E2895" t="n">
+        <v>822.86</v>
+      </c>
+      <c r="F2895" t="n">
+        <v>6.095</v>
+      </c>
+      <c r="G2895" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2896">
+      <c r="A2896" t="inlineStr">
+        <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="B2896" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="C2896" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2896" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2896" t="n">
+        <v>9.99</v>
+      </c>
+      <c r="F2896" t="n">
+        <v>4.995</v>
+      </c>
+      <c r="G2896" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2897">
+      <c r="A2897" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B2897" t="inlineStr">
+        <is>
+          <t>1116</t>
+        </is>
+      </c>
+      <c r="C2897" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2897" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2897" t="n">
+        <v>114.23</v>
+      </c>
+      <c r="F2897" t="n">
+        <v>6.719</v>
+      </c>
+      <c r="G2897" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2898">
+      <c r="A2898" t="inlineStr">
+        <is>
+          <t>2026-08-15</t>
+        </is>
+      </c>
+      <c r="B2898" t="inlineStr">
+        <is>
+          <t>4309</t>
+        </is>
+      </c>
+      <c r="C2898" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2898" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2898" t="n">
+        <v>1987</v>
+      </c>
+      <c r="F2898" t="n">
+        <v>496.75</v>
+      </c>
+      <c r="G2898" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2899">
+      <c r="A2899" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="B2899" t="inlineStr">
+        <is>
+          <t>5217</t>
+        </is>
+      </c>
+      <c r="C2899" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2899" t="n">
+        <v>62</v>
+      </c>
+      <c r="E2899" t="n">
+        <v>464.29</v>
+      </c>
+      <c r="F2899" t="n">
+        <v>7.489</v>
+      </c>
+      <c r="G2899" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2900">
+      <c r="A2900" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="B2900" t="inlineStr">
+        <is>
+          <t>5822</t>
+        </is>
+      </c>
+      <c r="C2900" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2900" t="n">
+        <v>184</v>
+      </c>
+      <c r="E2900" t="n">
+        <v>1232.54</v>
+      </c>
+      <c r="F2900" t="n">
+        <v>6.699</v>
+      </c>
+      <c r="G2900" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2901">
+      <c r="A2901" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B2901" t="inlineStr">
+        <is>
+          <t>5624</t>
+        </is>
+      </c>
+      <c r="C2901" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2901" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2901" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="F2901" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="G2901" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2902">
+      <c r="A2902" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B2902" t="inlineStr">
+        <is>
+          <t>1240</t>
+        </is>
+      </c>
+      <c r="C2902" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2902" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2902" t="n">
+        <v>93.73</v>
+      </c>
+      <c r="F2902" t="n">
+        <v>5.514</v>
+      </c>
+      <c r="G2902" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2903">
+      <c r="A2903" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B2903" t="inlineStr">
+        <is>
+          <t>2513</t>
+        </is>
+      </c>
+      <c r="C2903" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2903" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2903" t="n">
+        <v>279.67</v>
+      </c>
+      <c r="F2903" t="n">
+        <v>5.826</v>
+      </c>
+      <c r="G2903" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2904">
+      <c r="A2904" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B2904" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C2904" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2904" t="n">
+        <v>63</v>
+      </c>
+      <c r="E2904" t="n">
+        <v>518.59</v>
+      </c>
+      <c r="F2904" t="n">
+        <v>8.231999999999999</v>
+      </c>
+      <c r="G2904" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2905">
+      <c r="A2905" t="inlineStr">
+        <is>
+          <t>2026-08-19</t>
+        </is>
+      </c>
+      <c r="B2905" t="inlineStr">
+        <is>
+          <t>5440</t>
+        </is>
+      </c>
+      <c r="C2905" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2905" t="n">
+        <v>82</v>
+      </c>
+      <c r="E2905" t="n">
+        <v>389.42</v>
+      </c>
+      <c r="F2905" t="n">
+        <v>4.749</v>
+      </c>
+      <c r="G2905" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2905"/>
+  <dimension ref="A1:G2919"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85499,6 +85499,440 @@
         </is>
       </c>
     </row>
+    <row r="2906">
+      <c r="A2906" t="inlineStr">
+        <is>
+          <t>2026-08-20</t>
+        </is>
+      </c>
+      <c r="B2906" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C2906" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2906" t="n">
+        <v>16</v>
+      </c>
+      <c r="E2906" t="n">
+        <v>147.15</v>
+      </c>
+      <c r="F2906" t="n">
+        <v>9.196999999999999</v>
+      </c>
+      <c r="G2906" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2907">
+      <c r="A2907" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B2907" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C2907" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2907" t="n">
+        <v>81</v>
+      </c>
+      <c r="E2907" t="n">
+        <v>692.7</v>
+      </c>
+      <c r="F2907" t="n">
+        <v>8.552</v>
+      </c>
+      <c r="G2907" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2908">
+      <c r="A2908" t="inlineStr">
+        <is>
+          <t>2026-08-22</t>
+        </is>
+      </c>
+      <c r="B2908" t="inlineStr">
+        <is>
+          <t>5217</t>
+        </is>
+      </c>
+      <c r="C2908" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2908" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2908" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="F2908" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="G2908" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2909">
+      <c r="A2909" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B2909" t="inlineStr">
+        <is>
+          <t>4212</t>
+        </is>
+      </c>
+      <c r="C2909" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2909" t="n">
+        <v>112</v>
+      </c>
+      <c r="E2909" t="n">
+        <v>669.59</v>
+      </c>
+      <c r="F2909" t="n">
+        <v>5.978</v>
+      </c>
+      <c r="G2909" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2910">
+      <c r="A2910" t="inlineStr">
+        <is>
+          <t>2026-08-23</t>
+        </is>
+      </c>
+      <c r="B2910" t="inlineStr">
+        <is>
+          <t>5440</t>
+        </is>
+      </c>
+      <c r="C2910" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2910" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2910" t="n">
+        <v>15.58</v>
+      </c>
+      <c r="F2910" t="n">
+        <v>5.193</v>
+      </c>
+      <c r="G2910" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2911">
+      <c r="A2911" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B2911" t="inlineStr">
+        <is>
+          <t>4212</t>
+        </is>
+      </c>
+      <c r="C2911" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2911" t="n">
+        <v>36</v>
+      </c>
+      <c r="E2911" t="n">
+        <v>215.53</v>
+      </c>
+      <c r="F2911" t="n">
+        <v>5.987</v>
+      </c>
+      <c r="G2911" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2912">
+      <c r="A2912" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2912" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="C2912" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2912" t="n">
+        <v>72</v>
+      </c>
+      <c r="E2912" t="n">
+        <v>504.02</v>
+      </c>
+      <c r="F2912" t="n">
+        <v>7</v>
+      </c>
+      <c r="G2912" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2913">
+      <c r="A2913" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2913" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C2913" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2913" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2913" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="F2913" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="G2913" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2914">
+      <c r="A2914" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="B2914" t="inlineStr">
+        <is>
+          <t>5410</t>
+        </is>
+      </c>
+      <c r="C2914" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2914" t="n">
+        <v>61</v>
+      </c>
+      <c r="E2914" t="n">
+        <v>438.84</v>
+      </c>
+      <c r="F2914" t="n">
+        <v>7.194</v>
+      </c>
+      <c r="G2914" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2915">
+      <c r="A2915" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B2915" t="inlineStr">
+        <is>
+          <t>3107</t>
+        </is>
+      </c>
+      <c r="C2915" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2915" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2915" t="n">
+        <v>43.29</v>
+      </c>
+      <c r="F2915" t="n">
+        <v>7.215</v>
+      </c>
+      <c r="G2915" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2916">
+      <c r="A2916" t="inlineStr">
+        <is>
+          <t>2026-08-26</t>
+        </is>
+      </c>
+      <c r="B2916" t="inlineStr">
+        <is>
+          <t>5205</t>
+        </is>
+      </c>
+      <c r="C2916" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2916" t="n">
+        <v>89</v>
+      </c>
+      <c r="E2916" t="n">
+        <v>699.54</v>
+      </c>
+      <c r="F2916" t="n">
+        <v>7.86</v>
+      </c>
+      <c r="G2916" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2917">
+      <c r="A2917" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2917" t="inlineStr">
+        <is>
+          <t>1213</t>
+        </is>
+      </c>
+      <c r="C2917" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2917" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2917" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="F2917" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="G2917" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2918">
+      <c r="A2918" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="B2918" t="inlineStr">
+        <is>
+          <t>5702</t>
+        </is>
+      </c>
+      <c r="C2918" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2918" t="n">
+        <v>82</v>
+      </c>
+      <c r="E2918" t="n">
+        <v>585.76</v>
+      </c>
+      <c r="F2918" t="n">
+        <v>7.143</v>
+      </c>
+      <c r="G2918" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2919">
+      <c r="A2919" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="B2919" t="inlineStr">
+        <is>
+          <t>5306</t>
+        </is>
+      </c>
+      <c r="C2919" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2919" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2919" t="n">
+        <v>27.22</v>
+      </c>
+      <c r="F2919" t="n">
+        <v>6.805</v>
+      </c>
+      <c r="G2919" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2919"/>
+  <dimension ref="A1:G2926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -85933,6 +85933,223 @@
         </is>
       </c>
     </row>
+    <row r="2920">
+      <c r="A2920" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B2920" t="inlineStr">
+        <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="C2920" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2920" t="n">
+        <v>92</v>
+      </c>
+      <c r="E2920" t="n">
+        <v>654.22</v>
+      </c>
+      <c r="F2920" t="n">
+        <v>7.111</v>
+      </c>
+      <c r="G2920" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2921">
+      <c r="A2921" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="B2921" t="inlineStr">
+        <is>
+          <t>5407</t>
+        </is>
+      </c>
+      <c r="C2921" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2921" t="n">
+        <v>142</v>
+      </c>
+      <c r="E2921" t="n">
+        <v>1083.51</v>
+      </c>
+      <c r="F2921" t="n">
+        <v>7.63</v>
+      </c>
+      <c r="G2921" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2922">
+      <c r="A2922" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B2922" t="inlineStr">
+        <is>
+          <t>5611</t>
+        </is>
+      </c>
+      <c r="C2922" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2922" t="n">
+        <v>84</v>
+      </c>
+      <c r="E2922" t="n">
+        <v>531.9299999999999</v>
+      </c>
+      <c r="F2922" t="n">
+        <v>6.332</v>
+      </c>
+      <c r="G2922" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2923">
+      <c r="A2923" t="inlineStr">
+        <is>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="B2923" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="C2923" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2923" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2923" t="n">
+        <v>33.01</v>
+      </c>
+      <c r="F2923" t="n">
+        <v>8.252000000000001</v>
+      </c>
+      <c r="G2923" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2924">
+      <c r="A2924" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B2924" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="C2924" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2924" t="n">
+        <v>63</v>
+      </c>
+      <c r="E2924" t="n">
+        <v>354.37</v>
+      </c>
+      <c r="F2924" t="n">
+        <v>5.625</v>
+      </c>
+      <c r="G2924" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2925">
+      <c r="A2925" t="inlineStr">
+        <is>
+          <t>2026-09-04</t>
+        </is>
+      </c>
+      <c r="B2925" t="inlineStr">
+        <is>
+          <t>5702</t>
+        </is>
+      </c>
+      <c r="C2925" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2925" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2925" t="n">
+        <v>19.6</v>
+      </c>
+      <c r="F2925" t="n">
+        <v>6.533</v>
+      </c>
+      <c r="G2925" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2926">
+      <c r="A2926" t="inlineStr">
+        <is>
+          <t>2026-09-05</t>
+        </is>
+      </c>
+      <c r="B2926" t="inlineStr">
+        <is>
+          <t>5614</t>
+        </is>
+      </c>
+      <c r="C2926" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2926" t="n">
+        <v>63</v>
+      </c>
+      <c r="E2926" t="n">
+        <v>352.72</v>
+      </c>
+      <c r="F2926" t="n">
+        <v>5.599</v>
+      </c>
+      <c r="G2926" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2926"/>
+  <dimension ref="A1:G2932"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86150,6 +86150,192 @@
         </is>
       </c>
     </row>
+    <row r="2927">
+      <c r="A2927" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B2927" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="C2927" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2927" t="n">
+        <v>95</v>
+      </c>
+      <c r="E2927" t="n">
+        <v>599.9</v>
+      </c>
+      <c r="F2927" t="n">
+        <v>6.31</v>
+      </c>
+      <c r="G2927" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2928">
+      <c r="A2928" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="B2928" t="inlineStr">
+        <is>
+          <t>3109</t>
+        </is>
+      </c>
+      <c r="C2928" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2928" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2928" t="n">
+        <v>21.34</v>
+      </c>
+      <c r="F2928" t="n">
+        <v>7.11</v>
+      </c>
+      <c r="G2928" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2929">
+      <c r="A2929" t="inlineStr">
+        <is>
+          <t>2026-09-07</t>
+        </is>
+      </c>
+      <c r="B2929" t="inlineStr">
+        <is>
+          <t>2214</t>
+        </is>
+      </c>
+      <c r="C2929" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2929" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2929" t="n">
+        <v>15.32</v>
+      </c>
+      <c r="F2929" t="n">
+        <v>7.66</v>
+      </c>
+      <c r="G2929" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2930">
+      <c r="A2930" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2930" t="inlineStr">
+        <is>
+          <t>2307</t>
+        </is>
+      </c>
+      <c r="C2930" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2930" t="n">
+        <v>132</v>
+      </c>
+      <c r="E2930" t="n">
+        <v>799.86</v>
+      </c>
+      <c r="F2930" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="G2930" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2931">
+      <c r="A2931" t="inlineStr">
+        <is>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="B2931" t="inlineStr">
+        <is>
+          <t>5853</t>
+        </is>
+      </c>
+      <c r="C2931" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2931" t="n">
+        <v>68</v>
+      </c>
+      <c r="E2931" t="n">
+        <v>371.02</v>
+      </c>
+      <c r="F2931" t="n">
+        <v>5.456</v>
+      </c>
+      <c r="G2931" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2932">
+      <c r="A2932" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="B2932" t="inlineStr">
+        <is>
+          <t>5611</t>
+        </is>
+      </c>
+      <c r="C2932" t="inlineStr">
+        <is>
+          <t>r579</t>
+        </is>
+      </c>
+      <c r="D2932" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2932" t="n">
+        <v>14.34</v>
+      </c>
+      <c r="F2932" t="n">
+        <v>7.17</v>
+      </c>
+      <c r="G2932" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2932"/>
+  <dimension ref="A1:G2943"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -86336,6 +86336,347 @@
         </is>
       </c>
     </row>
+    <row r="2933">
+      <c r="A2933" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="B2933" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="C2933" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2933" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2933" t="n">
+        <v>17.72</v>
+      </c>
+      <c r="F2933" t="n">
+        <v>5.907</v>
+      </c>
+      <c r="G2933" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2934">
+      <c r="A2934" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2934" t="inlineStr">
+        <is>
+          <t>5852</t>
+        </is>
+      </c>
+      <c r="C2934" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2934" t="n">
+        <v>194</v>
+      </c>
+      <c r="E2934" t="n">
+        <v>1178.5</v>
+      </c>
+      <c r="F2934" t="n">
+        <v>6.075</v>
+      </c>
+      <c r="G2934" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2935">
+      <c r="A2935" t="inlineStr">
+        <is>
+          <t>2026-09-15</t>
+        </is>
+      </c>
+      <c r="B2935" t="inlineStr">
+        <is>
+          <t>5853</t>
+        </is>
+      </c>
+      <c r="C2935" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2935" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2935" t="n">
+        <v>20.1</v>
+      </c>
+      <c r="F2935" t="n">
+        <v>6.7</v>
+      </c>
+      <c r="G2935" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2936">
+      <c r="A2936" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2936" t="inlineStr">
+        <is>
+          <t>5852</t>
+        </is>
+      </c>
+      <c r="C2936" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2936" t="n">
+        <v>9</v>
+      </c>
+      <c r="E2936" t="n">
+        <v>54.08</v>
+      </c>
+      <c r="F2936" t="n">
+        <v>6.009</v>
+      </c>
+      <c r="G2936" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2937">
+      <c r="A2937" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="B2937" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="C2937" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2937" t="n">
+        <v>174</v>
+      </c>
+      <c r="E2937" t="n">
+        <v>1025.34</v>
+      </c>
+      <c r="F2937" t="n">
+        <v>5.893</v>
+      </c>
+      <c r="G2937" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2938">
+      <c r="A2938" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B2938" t="inlineStr">
+        <is>
+          <t>4301</t>
+        </is>
+      </c>
+      <c r="C2938" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2938" t="n">
+        <v>60</v>
+      </c>
+      <c r="E2938" t="n">
+        <v>478.32</v>
+      </c>
+      <c r="F2938" t="n">
+        <v>7.972</v>
+      </c>
+      <c r="G2938" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2939">
+      <c r="A2939" t="inlineStr">
+        <is>
+          <t>2026-09-12</t>
+        </is>
+      </c>
+      <c r="B2939" t="inlineStr">
+        <is>
+          <t>5854</t>
+        </is>
+      </c>
+      <c r="C2939" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2939" t="n">
+        <v>62</v>
+      </c>
+      <c r="E2939" t="n">
+        <v>331.42</v>
+      </c>
+      <c r="F2939" t="n">
+        <v>5.345</v>
+      </c>
+      <c r="G2939" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2940">
+      <c r="A2940" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="B2940" t="inlineStr">
+        <is>
+          <t>5208</t>
+        </is>
+      </c>
+      <c r="C2940" t="inlineStr">
+        <is>
+          <t>CO62175</t>
+        </is>
+      </c>
+      <c r="D2940" t="n">
+        <v>104</v>
+      </c>
+      <c r="E2940" t="n">
+        <v>655.6</v>
+      </c>
+      <c r="F2940" t="n">
+        <v>6.304</v>
+      </c>
+      <c r="G2940" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2941">
+      <c r="A2941" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="B2941" t="inlineStr">
+        <is>
+          <t>5702</t>
+        </is>
+      </c>
+      <c r="C2941" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2941" t="n">
+        <v>176</v>
+      </c>
+      <c r="E2941" t="n">
+        <v>1170.94</v>
+      </c>
+      <c r="F2941" t="n">
+        <v>6.653</v>
+      </c>
+      <c r="G2941" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2942">
+      <c r="A2942" t="inlineStr">
+        <is>
+          <t>2026-09-19</t>
+        </is>
+      </c>
+      <c r="B2942" t="inlineStr">
+        <is>
+          <t>5623</t>
+        </is>
+      </c>
+      <c r="C2942" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2942" t="n">
+        <v>20</v>
+      </c>
+      <c r="E2942" t="n">
+        <v>107.54</v>
+      </c>
+      <c r="F2942" t="n">
+        <v>5.377</v>
+      </c>
+      <c r="G2942" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2943">
+      <c r="A2943" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B2943" t="inlineStr">
+        <is>
+          <t>5623</t>
+        </is>
+      </c>
+      <c r="C2943" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2943" t="n">
+        <v>55</v>
+      </c>
+      <c r="E2943" t="n">
+        <v>291.8</v>
+      </c>
+      <c r="F2943" t="n">
+        <v>5.305</v>
+      </c>
+      <c r="G2943" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2967"/>
+  <dimension ref="A1:G2976"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87421,6 +87421,285 @@
         </is>
       </c>
     </row>
+    <row r="2968">
+      <c r="A2968" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2968" t="inlineStr">
+        <is>
+          <t>4215</t>
+        </is>
+      </c>
+      <c r="C2968" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2968" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2968" t="n">
+        <v>79.7</v>
+      </c>
+      <c r="F2968" t="n">
+        <v>6.642</v>
+      </c>
+      <c r="G2968" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2969">
+      <c r="A2969" t="inlineStr">
+        <is>
+          <t>2026-10-06</t>
+        </is>
+      </c>
+      <c r="B2969" t="inlineStr">
+        <is>
+          <t>5404</t>
+        </is>
+      </c>
+      <c r="C2969" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2969" t="n">
+        <v>6</v>
+      </c>
+      <c r="E2969" t="n">
+        <v>39.4</v>
+      </c>
+      <c r="F2969" t="n">
+        <v>6.567</v>
+      </c>
+      <c r="G2969" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2970">
+      <c r="A2970" t="inlineStr">
+        <is>
+          <t>2026-10-07</t>
+        </is>
+      </c>
+      <c r="B2970" t="inlineStr">
+        <is>
+          <t>2516</t>
+        </is>
+      </c>
+      <c r="C2970" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2970" t="n">
+        <v>130</v>
+      </c>
+      <c r="E2970" t="n">
+        <v>735.52</v>
+      </c>
+      <c r="F2970" t="n">
+        <v>5.658</v>
+      </c>
+      <c r="G2970" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2971">
+      <c r="A2971" t="inlineStr">
+        <is>
+          <t>2026-10-08</t>
+        </is>
+      </c>
+      <c r="B2971" t="inlineStr">
+        <is>
+          <t>5663</t>
+        </is>
+      </c>
+      <c r="C2971" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2971" t="n">
+        <v>53</v>
+      </c>
+      <c r="E2971" t="n">
+        <v>347.64</v>
+      </c>
+      <c r="F2971" t="n">
+        <v>6.559</v>
+      </c>
+      <c r="G2971" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2972">
+      <c r="A2972" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="B2972" t="inlineStr">
+        <is>
+          <t>5663</t>
+        </is>
+      </c>
+      <c r="C2972" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2972" t="n">
+        <v>113</v>
+      </c>
+      <c r="E2972" t="n">
+        <v>740.7</v>
+      </c>
+      <c r="F2972" t="n">
+        <v>6.555</v>
+      </c>
+      <c r="G2972" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2973">
+      <c r="A2973" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="B2973" t="inlineStr">
+        <is>
+          <t>3411</t>
+        </is>
+      </c>
+      <c r="C2973" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2973" t="n">
+        <v>125</v>
+      </c>
+      <c r="E2973" t="n">
+        <v>816.4</v>
+      </c>
+      <c r="F2973" t="n">
+        <v>6.531</v>
+      </c>
+      <c r="G2973" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2974">
+      <c r="A2974" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B2974" t="inlineStr">
+        <is>
+          <t>5460</t>
+        </is>
+      </c>
+      <c r="C2974" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2974" t="n">
+        <v>84</v>
+      </c>
+      <c r="E2974" t="n">
+        <v>520.22</v>
+      </c>
+      <c r="F2974" t="n">
+        <v>6.193</v>
+      </c>
+      <c r="G2974" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2975">
+      <c r="A2975" t="inlineStr">
+        <is>
+          <t>2026-10-14</t>
+        </is>
+      </c>
+      <c r="B2975" t="inlineStr">
+        <is>
+          <t>5460</t>
+        </is>
+      </c>
+      <c r="C2975" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2975" t="n">
+        <v>13</v>
+      </c>
+      <c r="E2975" t="n">
+        <v>67.22</v>
+      </c>
+      <c r="F2975" t="n">
+        <v>5.171</v>
+      </c>
+      <c r="G2975" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2976">
+      <c r="A2976" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="B2976" t="inlineStr">
+        <is>
+          <t>1212</t>
+        </is>
+      </c>
+      <c r="C2976" t="inlineStr">
+        <is>
+          <t>R570</t>
+        </is>
+      </c>
+      <c r="D2976" t="n">
+        <v>12</v>
+      </c>
+      <c r="E2976" t="n">
+        <v>65.88</v>
+      </c>
+      <c r="F2976" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="G2976" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2976"/>
+  <dimension ref="A1:G2986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -87700,6 +87700,316 @@
         </is>
       </c>
     </row>
+    <row r="2977">
+      <c r="A2977" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B2977" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="C2977" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2977" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2977" t="n">
+        <v>116.1</v>
+      </c>
+      <c r="F2977" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="G2977" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2978">
+      <c r="A2978" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="B2978" t="inlineStr">
+        <is>
+          <t>5833</t>
+        </is>
+      </c>
+      <c r="C2978" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2978" t="n">
+        <v>94</v>
+      </c>
+      <c r="E2978" t="n">
+        <v>538.0599999999999</v>
+      </c>
+      <c r="F2978" t="n">
+        <v>5.724</v>
+      </c>
+      <c r="G2978" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2979">
+      <c r="A2979" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2979" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="C2979" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2979" t="n">
+        <v>48</v>
+      </c>
+      <c r="E2979" t="n">
+        <v>234.3</v>
+      </c>
+      <c r="F2979" t="n">
+        <v>4.881</v>
+      </c>
+      <c r="G2979" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2980">
+      <c r="A2980" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2980" t="inlineStr">
+        <is>
+          <t>4226</t>
+        </is>
+      </c>
+      <c r="C2980" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2980" t="n">
+        <v>66</v>
+      </c>
+      <c r="E2980" t="n">
+        <v>337.48</v>
+      </c>
+      <c r="F2980" t="n">
+        <v>5.113</v>
+      </c>
+      <c r="G2980" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2981">
+      <c r="A2981" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2981" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="C2981" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2981" t="n">
+        <v>176</v>
+      </c>
+      <c r="E2981" t="n">
+        <v>1132.38</v>
+      </c>
+      <c r="F2981" t="n">
+        <v>6.434</v>
+      </c>
+      <c r="G2981" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2982">
+      <c r="A2982" t="inlineStr">
+        <is>
+          <t>2026-10-19</t>
+        </is>
+      </c>
+      <c r="B2982" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="C2982" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2982" t="n">
+        <v>50</v>
+      </c>
+      <c r="E2982" t="n">
+        <v>302.26</v>
+      </c>
+      <c r="F2982" t="n">
+        <v>6.045</v>
+      </c>
+      <c r="G2982" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2983">
+      <c r="A2983" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2983" t="inlineStr">
+        <is>
+          <t>3417</t>
+        </is>
+      </c>
+      <c r="C2983" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2983" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2983" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="F2983" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="G2983" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2984">
+      <c r="A2984" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2984" t="inlineStr">
+        <is>
+          <t>4226</t>
+        </is>
+      </c>
+      <c r="C2984" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2984" t="n">
+        <v>18</v>
+      </c>
+      <c r="E2984" t="n">
+        <v>87.73999999999999</v>
+      </c>
+      <c r="F2984" t="n">
+        <v>4.874</v>
+      </c>
+      <c r="G2984" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2985">
+      <c r="A2985" t="inlineStr">
+        <is>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="B2985" t="inlineStr">
+        <is>
+          <t>5832</t>
+        </is>
+      </c>
+      <c r="C2985" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2985" t="n">
+        <v>144</v>
+      </c>
+      <c r="E2985" t="n">
+        <v>867.8</v>
+      </c>
+      <c r="F2985" t="n">
+        <v>6.026</v>
+      </c>
+      <c r="G2985" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2986">
+      <c r="A2986" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="B2986" t="inlineStr">
+        <is>
+          <t>5418</t>
+        </is>
+      </c>
+      <c r="C2986" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2986" t="n">
+        <v>11</v>
+      </c>
+      <c r="E2986" t="n">
+        <v>60.56</v>
+      </c>
+      <c r="F2986" t="n">
+        <v>5.505</v>
+      </c>
+      <c r="G2986" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2986"/>
+  <dimension ref="A1:G3002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88010,6 +88010,502 @@
         </is>
       </c>
     </row>
+    <row r="2987">
+      <c r="A2987" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2987" t="inlineStr">
+        <is>
+          <t>4334</t>
+        </is>
+      </c>
+      <c r="C2987" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2987" t="n">
+        <v>56</v>
+      </c>
+      <c r="E2987" t="n">
+        <v>340.76</v>
+      </c>
+      <c r="F2987" t="n">
+        <v>6.085</v>
+      </c>
+      <c r="G2987" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2988">
+      <c r="A2988" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2988" t="inlineStr">
+        <is>
+          <t>4226</t>
+        </is>
+      </c>
+      <c r="C2988" t="inlineStr">
+        <is>
+          <t>97F1692</t>
+        </is>
+      </c>
+      <c r="D2988" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2988" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="F2988" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="G2988" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2989">
+      <c r="A2989" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2989" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C2989" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2989" t="n">
+        <v>29</v>
+      </c>
+      <c r="E2989" t="n">
+        <v>191.88</v>
+      </c>
+      <c r="F2989" t="n">
+        <v>6.617</v>
+      </c>
+      <c r="G2989" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2990">
+      <c r="A2990" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2990" t="inlineStr">
+        <is>
+          <t>1238</t>
+        </is>
+      </c>
+      <c r="C2990" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2990" t="n">
+        <v>86</v>
+      </c>
+      <c r="E2990" t="n">
+        <v>548.28</v>
+      </c>
+      <c r="F2990" t="n">
+        <v>6.375</v>
+      </c>
+      <c r="G2990" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2991">
+      <c r="A2991" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2991" t="inlineStr">
+        <is>
+          <t>2515</t>
+        </is>
+      </c>
+      <c r="C2991" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2991" t="n">
+        <v>46</v>
+      </c>
+      <c r="E2991" t="n">
+        <v>336.24</v>
+      </c>
+      <c r="F2991" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="G2991" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2992">
+      <c r="A2992" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2992" t="inlineStr">
+        <is>
+          <t>5107</t>
+        </is>
+      </c>
+      <c r="C2992" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2992" t="n">
+        <v>124</v>
+      </c>
+      <c r="E2992" t="n">
+        <v>1057.24</v>
+      </c>
+      <c r="F2992" t="n">
+        <v>8.526</v>
+      </c>
+      <c r="G2992" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2993">
+      <c r="A2993" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2993" t="inlineStr">
+        <is>
+          <t>5203</t>
+        </is>
+      </c>
+      <c r="C2993" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2993" t="n">
+        <v>1</v>
+      </c>
+      <c r="E2993" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="F2993" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="G2993" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2994">
+      <c r="A2994" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B2994" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="C2994" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2994" t="n">
+        <v>3</v>
+      </c>
+      <c r="E2994" t="n">
+        <v>16.16</v>
+      </c>
+      <c r="F2994" t="n">
+        <v>5.387</v>
+      </c>
+      <c r="G2994" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2995">
+      <c r="A2995" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2995" t="inlineStr">
+        <is>
+          <t>1123</t>
+        </is>
+      </c>
+      <c r="C2995" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2995" t="n">
+        <v>17</v>
+      </c>
+      <c r="E2995" t="n">
+        <v>133.96</v>
+      </c>
+      <c r="F2995" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="G2995" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2996">
+      <c r="A2996" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2996" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C2996" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2996" t="n">
+        <v>4</v>
+      </c>
+      <c r="E2996" t="n">
+        <v>25.94</v>
+      </c>
+      <c r="F2996" t="n">
+        <v>6.485</v>
+      </c>
+      <c r="G2996" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2997">
+      <c r="A2997" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2997" t="inlineStr">
+        <is>
+          <t>2515</t>
+        </is>
+      </c>
+      <c r="C2997" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2997" t="n">
+        <v>52</v>
+      </c>
+      <c r="E2997" t="n">
+        <v>391.3</v>
+      </c>
+      <c r="F2997" t="n">
+        <v>7.525</v>
+      </c>
+      <c r="G2997" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2998">
+      <c r="A2998" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2998" t="inlineStr">
+        <is>
+          <t>5107</t>
+        </is>
+      </c>
+      <c r="C2998" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2998" t="n">
+        <v>37</v>
+      </c>
+      <c r="E2998" t="n">
+        <v>315.42</v>
+      </c>
+      <c r="F2998" t="n">
+        <v>8.525</v>
+      </c>
+      <c r="G2998" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="2999">
+      <c r="A2999" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B2999" t="inlineStr">
+        <is>
+          <t>5439</t>
+        </is>
+      </c>
+      <c r="C2999" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D2999" t="n">
+        <v>2</v>
+      </c>
+      <c r="E2999" t="n">
+        <v>11.24</v>
+      </c>
+      <c r="F2999" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="G2999" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3000">
+      <c r="A3000" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B3000" t="inlineStr">
+        <is>
+          <t>1236</t>
+        </is>
+      </c>
+      <c r="C3000" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D3000" t="n">
+        <v>1</v>
+      </c>
+      <c r="E3000" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="F3000" t="n">
+        <v>12.44</v>
+      </c>
+      <c r="G3000" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3001">
+      <c r="A3001" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B3001" t="inlineStr">
+        <is>
+          <t>1238</t>
+        </is>
+      </c>
+      <c r="C3001" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D3001" t="n">
+        <v>5</v>
+      </c>
+      <c r="E3001" t="n">
+        <v>33.18</v>
+      </c>
+      <c r="F3001" t="n">
+        <v>6.636</v>
+      </c>
+      <c r="G3001" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3002">
+      <c r="A3002" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B3002" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="C3002" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D3002" t="n">
+        <v>34</v>
+      </c>
+      <c r="E3002" t="n">
+        <v>222.7</v>
+      </c>
+      <c r="F3002" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="G3002" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/mill_return.xlsx
+++ b/data/mill_return.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3002"/>
+  <dimension ref="A1:G3003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -88506,6 +88506,37 @@
         </is>
       </c>
     </row>
+    <row r="3003">
+      <c r="A3003" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B3003" t="inlineStr">
+        <is>
+          <t>5219</t>
+        </is>
+      </c>
+      <c r="C3003" t="inlineStr">
+        <is>
+          <t>R579</t>
+        </is>
+      </c>
+      <c r="D3003" t="n">
+        <v>147</v>
+      </c>
+      <c r="E3003" t="n">
+        <v>1033.84</v>
+      </c>
+      <c r="F3003" t="n">
+        <v>7.033</v>
+      </c>
+      <c r="G3003" t="inlineStr">
+        <is>
+          <t>2026/27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
